--- a/tenders/ГРК — карьерный сайт/02-estimate/ТКП_ГРК_AIR.xlsx
+++ b/tenders/ГРК — карьерный сайт/02-estimate/ТКП_ГРК_AIR.xlsx
@@ -3976,12 +3976,12 @@
       </c>
       <c r="E16" s="128">
         <f>SUM(E17:E18)</f>
-        <v>106.8</v>
+        <v>84.28571428571429</v>
       </c>
       <c r="F16" s="129"/>
       <c r="G16" s="130">
         <f>SUM(G17:G18)</f>
-        <v>373800</v>
+        <v>295000</v>
       </c>
       <c r="H16" s="131">
         <v>7</v>
@@ -3998,14 +3998,14 @@
         <v>141</v>
       </c>
       <c r="E17" s="133">
-        <v>70.2</v>
+        <v>55.371428571428574</v>
       </c>
       <c r="F17" s="129">
         <v>3500</v>
       </c>
       <c r="G17" s="134">
         <f>F17*E17</f>
-        <v>245700</v>
+        <v>193800</v>
       </c>
       <c r="H17" s="131"/>
     </row>
@@ -4020,14 +4020,14 @@
         <v>141</v>
       </c>
       <c r="E18" s="133">
-        <v>36.6</v>
+        <v>28.914285714285715</v>
       </c>
       <c r="F18" s="129">
         <v>3500</v>
       </c>
       <c r="G18" s="134">
         <f>F18*E18</f>
-        <v>128100</v>
+        <v>101200</v>
       </c>
       <c r="H18" s="131"/>
     </row>
@@ -4043,12 +4043,12 @@
       </c>
       <c r="E19" s="128">
         <f>SUM(E20:E21)</f>
-        <v>106.8</v>
+        <v>84.28571428571429</v>
       </c>
       <c r="F19" s="129"/>
       <c r="G19" s="130">
         <f>SUM(G20:G21)</f>
-        <v>373800</v>
+        <v>295000</v>
       </c>
       <c r="H19" s="131">
         <v>7</v>
@@ -4065,14 +4065,14 @@
         <v>141</v>
       </c>
       <c r="E20" s="133">
-        <v>70.2</v>
+        <v>55.371428571428574</v>
       </c>
       <c r="F20" s="129">
         <v>3500</v>
       </c>
       <c r="G20" s="134">
         <f>F20*E20</f>
-        <v>245700</v>
+        <v>193800</v>
       </c>
       <c r="H20" s="131"/>
     </row>
@@ -4087,14 +4087,14 @@
         <v>141</v>
       </c>
       <c r="E21" s="133">
-        <v>36.6</v>
+        <v>28.914285714285715</v>
       </c>
       <c r="F21" s="129">
         <v>3500</v>
       </c>
       <c r="G21" s="134">
         <f>F21*E21</f>
-        <v>128100</v>
+        <v>101200</v>
       </c>
       <c r="H21" s="131"/>
     </row>
@@ -4110,12 +4110,12 @@
       </c>
       <c r="E22" s="128">
         <f>SUM(E23:E24)</f>
-        <v>213.5</v>
+        <v>168.28571428571428</v>
       </c>
       <c r="F22" s="129"/>
       <c r="G22" s="130">
         <f>SUM(G23:G24)</f>
-        <v>747250</v>
+        <v>589000</v>
       </c>
       <c r="H22" s="131">
         <v>14</v>
@@ -4132,14 +4132,14 @@
         <v>141</v>
       </c>
       <c r="E23" s="133">
-        <v>140.3</v>
+        <v>110.54285714285714</v>
       </c>
       <c r="F23" s="129">
         <v>3500</v>
       </c>
       <c r="G23" s="134">
         <f>F23*E23</f>
-        <v>491050</v>
+        <v>386900</v>
       </c>
       <c r="H23" s="131"/>
     </row>
@@ -4154,14 +4154,14 @@
         <v>141</v>
       </c>
       <c r="E24" s="133">
-        <v>73.2</v>
+        <v>57.74285714285714</v>
       </c>
       <c r="F24" s="129">
         <v>3500</v>
       </c>
       <c r="G24" s="134">
         <f>F24*E24</f>
-        <v>256200</v>
+        <v>202100</v>
       </c>
       <c r="H24" s="131"/>
     </row>
@@ -4177,12 +4177,12 @@
       </c>
       <c r="E25" s="128">
         <f>SUM(E26:E28)</f>
-        <v>1281.3</v>
+        <v>1010.5714285714286</v>
       </c>
       <c r="F25" s="129"/>
       <c r="G25" s="130">
         <f>SUM(G26:G28)</f>
-        <v>4484550</v>
+        <v>3537000</v>
       </c>
       <c r="H25" s="131">
         <v>84</v>
@@ -4199,14 +4199,14 @@
         <v>141</v>
       </c>
       <c r="E26" s="133">
-        <v>533.8</v>
+        <v>421.0857142857143</v>
       </c>
       <c r="F26" s="129">
         <v>3500</v>
       </c>
       <c r="G26" s="134">
         <f>F26*E26</f>
-        <v>1868300</v>
+        <v>1473800</v>
       </c>
       <c r="H26" s="131"/>
     </row>
@@ -4221,14 +4221,14 @@
         <v>141</v>
       </c>
       <c r="E27" s="133">
-        <v>426.9</v>
+        <v>336.7142857142857</v>
       </c>
       <c r="F27" s="129">
         <v>3500</v>
       </c>
       <c r="G27" s="134">
         <f>F27*E27</f>
-        <v>1494150</v>
+        <v>1178500</v>
       </c>
       <c r="H27" s="131"/>
     </row>
@@ -4243,14 +4243,14 @@
         <v>141</v>
       </c>
       <c r="E28" s="133">
-        <v>320.6</v>
+        <v>252.77142857142857</v>
       </c>
       <c r="F28" s="129">
         <v>3500</v>
       </c>
       <c r="G28" s="134">
         <f>F28*E28</f>
-        <v>1122100</v>
+        <v>884700</v>
       </c>
       <c r="H28" s="131"/>
     </row>
@@ -4266,12 +4266,12 @@
       </c>
       <c r="E29" s="128">
         <f>SUM(E30:E31)</f>
-        <v>106.8</v>
+        <v>84.28571428571429</v>
       </c>
       <c r="F29" s="129"/>
       <c r="G29" s="130">
         <f>SUM(G30:G31)</f>
-        <v>373800</v>
+        <v>295000</v>
       </c>
       <c r="H29" s="131">
         <v>7</v>
@@ -4288,14 +4288,14 @@
         <v>141</v>
       </c>
       <c r="E30" s="133">
-        <v>70.2</v>
+        <v>55.371428571428574</v>
       </c>
       <c r="F30" s="129">
         <v>3500</v>
       </c>
       <c r="G30" s="134">
         <f>F30*E30</f>
-        <v>245700</v>
+        <v>193800</v>
       </c>
       <c r="H30" s="131"/>
     </row>
@@ -4310,14 +4310,14 @@
         <v>141</v>
       </c>
       <c r="E31" s="133">
-        <v>36.6</v>
+        <v>28.914285714285715</v>
       </c>
       <c r="F31" s="129">
         <v>3500</v>
       </c>
       <c r="G31" s="134">
         <f>F31*E31</f>
-        <v>128100</v>
+        <v>101200</v>
       </c>
       <c r="H31" s="131"/>
     </row>
@@ -4333,12 +4333,12 @@
       </c>
       <c r="E32" s="128">
         <f>SUM(E33:E34)</f>
-        <v>106.8</v>
+        <v>84.28571428571429</v>
       </c>
       <c r="F32" s="129"/>
       <c r="G32" s="130">
         <f>SUM(G33:G34)</f>
-        <v>373800</v>
+        <v>295000</v>
       </c>
       <c r="H32" s="131">
         <v>7</v>
@@ -4355,14 +4355,14 @@
         <v>141</v>
       </c>
       <c r="E33" s="133">
-        <v>70.2</v>
+        <v>55.371428571428574</v>
       </c>
       <c r="F33" s="129">
         <v>3500</v>
       </c>
       <c r="G33" s="134">
         <f>F33*E33</f>
-        <v>245700</v>
+        <v>193800</v>
       </c>
       <c r="H33" s="131"/>
     </row>
@@ -4377,14 +4377,14 @@
         <v>141</v>
       </c>
       <c r="E34" s="133">
-        <v>36.6</v>
+        <v>28.914285714285715</v>
       </c>
       <c r="F34" s="129">
         <v>3500</v>
       </c>
       <c r="G34" s="134">
         <f>F34*E34</f>
-        <v>128100</v>
+        <v>101200</v>
       </c>
       <c r="H34" s="131"/>
     </row>
@@ -4400,12 +4400,12 @@
       </c>
       <c r="E35" s="128">
         <f>SUM(E36:E37)</f>
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="F35" s="129"/>
       <c r="G35" s="130">
         <f>SUM(G36:G37)</f>
-        <v>213500</v>
+        <v>168000</v>
       </c>
       <c r="H35" s="131">
         <v>4</v>
@@ -4422,14 +4422,14 @@
         <v>141</v>
       </c>
       <c r="E36" s="133">
-        <v>39.1</v>
+        <v>30.771428571428572</v>
       </c>
       <c r="F36" s="129">
         <v>3500</v>
       </c>
       <c r="G36" s="134">
         <f>F36*E36</f>
-        <v>136850</v>
+        <v>107700</v>
       </c>
       <c r="H36" s="131"/>
     </row>
@@ -4444,14 +4444,14 @@
         <v>141</v>
       </c>
       <c r="E37" s="133">
-        <v>21.9</v>
+        <v>17.228571428571428</v>
       </c>
       <c r="F37" s="129">
         <v>3500</v>
       </c>
       <c r="G37" s="134">
         <f>F37*E37</f>
-        <v>76650</v>
+        <v>60300</v>
       </c>
       <c r="H37" s="131"/>
     </row>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="E38" s="128">
         <f>SUM(E39:E40)</f>
-        <v>45.571429</v>
+        <v>36</v>
       </c>
       <c r="F38" s="129"/>
       <c r="G38" s="130">
         <f>SUM(G39:G40)</f>
-        <v>159500</v>
+        <v>126000</v>
       </c>
       <c r="H38" s="131">
         <v>3</v>
@@ -4489,14 +4489,14 @@
         <v>141</v>
       </c>
       <c r="E39" s="133">
-        <v>27.5</v>
+        <v>21.714285714285715</v>
       </c>
       <c r="F39" s="129">
         <v>3500</v>
       </c>
       <c r="G39" s="134">
         <f>F39*E39</f>
-        <v>96250</v>
+        <v>76000</v>
       </c>
       <c r="H39" s="131"/>
     </row>
@@ -4511,14 +4511,14 @@
         <v>141</v>
       </c>
       <c r="E40" s="133">
-        <v>18.071429</v>
+        <v>14.285714285714286</v>
       </c>
       <c r="F40" s="129">
         <v>3500</v>
       </c>
       <c r="G40" s="134">
         <f>F40*E40</f>
-        <v>63250</v>
+        <v>50000</v>
       </c>
       <c r="H40" s="131"/>
     </row>
@@ -4530,12 +4530,12 @@
       <c r="D41" s="137"/>
       <c r="E41" s="133">
         <f>E25+E29+E32+E35+E38+E22+E19+E16</f>
-        <v>2028.571429</v>
+        <v>1600</v>
       </c>
       <c r="F41" s="138"/>
       <c r="G41" s="139">
         <f>+G25+G29+G32+G35+G38+G22+G19+G16</f>
-        <v>7100000</v>
+        <v>5600000</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
